--- a/astro-site/public/dl/catering-business-plan/catering-startup-checklist.xlsx
+++ b/astro-site/public/dl/catering-business-plan/catering-startup-checklist.xlsx
@@ -625,12 +625,12 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Get your EIN from the IRS and register for state payroll and unemployment tax</t>
+          <t>File your LLC with the Secretary of State and appoint a registered agent</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Owner / Attorney</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>The EIN is free and takes minutes online at irs.gov. Register with your state workforce agency before your first hire, so your payroll provider can file from day one.</t>
+          <t>File the articles of organization and sign an operating agreement, even for a single-member LLC. Filing fees and processing times vary by state; check the state website.</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>File your LLC with the Secretary of State and appoint a registered agent</t>
+          <t>Get your EIN from the IRS and register for state payroll and unemployment tax</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Owner / Attorney</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Weeks 1-3</t>
+          <t>Weeks 2-3</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>File the articles of organization and sign an operating agreement, even for a single-member LLC. Filing fees and processing times vary by state; check the state website.</t>
+          <t>Apply once the state approves your LLC. The EIN is free and takes minutes online at irs.gov. Register with your state workforce agency before your first hire, so your payroll provider can file from day one.</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>The health department requires it. It should name your hours, storage areas, parking and cleaning duties. Keep a copy for the permit application.</t>
+          <t>Most health departments ask for it with the permit application. It should name your hours, storage areas, parking and cleaning duties; keep a signed copy on file.</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Plan review applies mainly if you lease your own kitchen. Expect an application, a fee, a menu review and an inspection of the kitchen and the van.</t>
+          <t>Many counties review your catering SOPs and charge a plan review fee before issuing the permit; a full plan review applies if you lease your own kitchen. Expect an application, a fee, a menu review and an inspection of the kitchen and the van.</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Buy general liability and business owner's policy coverage, and order certificates of insurance</t>
+          <t>Buy general liability (or a business owner's policy) and order certificates of insurance</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Open accounts with a broadline distributor (US Foods, Sysco, Restaurant Depot)</t>
+          <t>Open accounts with a broadline distributor (US Foods, Sysco) and a cash-and-carry such as Restaurant Depot</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -2135,7 +2135,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="59.75" customHeight="1">
+    <row r="14" ht="74.75" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
           <t>☐</t>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>A mandatory service charge is wages (IRS Rev. Rul. 2012-18); a gratuity is voluntary and goes to staff. Keep them on separate invoice lines and check your state's sales tax rule.</t>
+          <t>A mandatory service charge is not a tip: the part paid out to staff is wages (IRS Rev. Rul. 2012-18). A gratuity is voluntary and goes to staff. Keep them on separate invoice lines and check your state's sales tax rule.</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Invoice the balance and collect within 24-48 hours; track deposits</t>
+          <t>Send the final invoice within 48 hours; track deposits and balances</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Send the final invoice right away, including any overages. Match deposits received against your quote and chase unpaid balances early.</t>
+          <t>Private clients usually pay the balance 5-7 days before the event; invoice overages within 48 hours and follow corporate invoices on their 30-day terms.</t>
         </is>
       </c>
     </row>
